--- a/data/05_modelado/results/results_mlp_ebm.xlsx
+++ b/data/05_modelado/results/results_mlp_ebm.xlsx
@@ -533,7 +533,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>EBM</t>
+          <t>MLP</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -547,61 +547,61 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.7671836754230297</v>
+        <v>0.813205080862484</v>
       </c>
       <c r="E2" t="n">
-        <v>0.007072489870372478</v>
+        <v>0.002406446270486991</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9202268779529679</v>
+        <v>0.9464621706301779</v>
       </c>
       <c r="G2" t="n">
-        <v>0.003602000107884734</v>
+        <v>0.002383645514213897</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8340643750835186</v>
+        <v>0.8772146191398633</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7105242453053473</v>
+        <v>0.7585815593670509</v>
       </c>
       <c r="J2" t="n">
-        <v>0.8739216670087654</v>
+        <v>0.8980889055676384</v>
       </c>
       <c r="K2" t="n">
-        <v>263.372</v>
+        <v>6.195</v>
       </c>
       <c r="L2" t="n">
-        <v>5.01</v>
+        <v>6.91</v>
       </c>
       <c r="M2" t="n">
-        <v>0.7719</v>
+        <v>0.8310999999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>0.9255</v>
+        <v>0.9530999999999999</v>
       </c>
       <c r="O2" t="n">
-        <v>0.8746</v>
+        <v>0.9165</v>
       </c>
       <c r="P2" t="n">
-        <v>0.8354</v>
+        <v>0.8512999999999999</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.7173</v>
+        <v>0.8119</v>
       </c>
       <c r="R2" t="n">
-        <v>0.876</v>
+        <v>0.9035</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6874</v>
+        <v>0.7635999999999999</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2971</v>
+        <v>0.2423</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>EBM</t>
+          <t>MLP</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -615,55 +615,55 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.7671836754230297</v>
+        <v>0.813205080862484</v>
       </c>
       <c r="E3" t="n">
-        <v>0.007072489870372478</v>
+        <v>0.002406446270486991</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9202268779529679</v>
+        <v>0.9464621706301779</v>
       </c>
       <c r="G3" t="n">
-        <v>0.003602000107884734</v>
+        <v>0.002383645514213897</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8340643750835186</v>
+        <v>0.8772146191398633</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7105242453053473</v>
+        <v>0.7585815593670509</v>
       </c>
       <c r="J3" t="n">
-        <v>0.8739216670087654</v>
+        <v>0.8980889055676384</v>
       </c>
       <c r="K3" t="n">
-        <v>265.606</v>
+        <v>6.972</v>
       </c>
       <c r="L3" t="n">
-        <v>5.01</v>
+        <v>6.65</v>
       </c>
       <c r="M3" t="n">
-        <v>0.7719</v>
+        <v>0.8310999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>0.9255</v>
+        <v>0.9530999999999999</v>
       </c>
       <c r="O3" t="n">
-        <v>0.8746</v>
+        <v>0.9165</v>
       </c>
       <c r="P3" t="n">
-        <v>0.8354</v>
+        <v>0.8512999999999999</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.7173</v>
+        <v>0.8119</v>
       </c>
       <c r="R3" t="n">
-        <v>0.876</v>
+        <v>0.9035</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6874</v>
+        <v>0.7635999999999999</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2971</v>
+        <v>0.2423</v>
       </c>
     </row>
     <row r="4">
@@ -683,55 +683,55 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.7742913987501752</v>
+        <v>0.8087287022616166</v>
       </c>
       <c r="E4" t="n">
-        <v>0.005569902515071754</v>
+        <v>0.004188423177670716</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9195671996866903</v>
+        <v>0.9379721344826782</v>
       </c>
       <c r="G4" t="n">
-        <v>0.004724682936439577</v>
+        <v>0.003904515896731891</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8145387034019862</v>
+        <v>0.8398505034006488</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7381117669439259</v>
+        <v>0.7800661738631012</v>
       </c>
       <c r="J4" t="n">
-        <v>0.8741446600472302</v>
+        <v>0.8920655709833989</v>
       </c>
       <c r="K4" t="n">
-        <v>840.438</v>
+        <v>1777.304</v>
       </c>
       <c r="L4" t="n">
-        <v>5.01</v>
+        <v>6.65</v>
       </c>
       <c r="M4" t="n">
-        <v>0.783</v>
+        <v>0.8099</v>
       </c>
       <c r="N4" t="n">
-        <v>0.9243</v>
+        <v>0.9422</v>
       </c>
       <c r="O4" t="n">
-        <v>0.8711</v>
+        <v>0.8953</v>
       </c>
       <c r="P4" t="n">
-        <v>0.8167</v>
+        <v>0.8349</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.7519</v>
+        <v>0.7865</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8781</v>
+        <v>0.892</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6984</v>
+        <v>0.7347</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3022</v>
+        <v>0.2665</v>
       </c>
     </row>
     <row r="5">
@@ -742,7 +742,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>smote</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -751,66 +751,66 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.7638435817419618</v>
+        <v>0.807845391480854</v>
       </c>
       <c r="E5" t="n">
-        <v>0.007048004886076593</v>
+        <v>0.01031190045657124</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9184766557449542</v>
+        <v>0.937399108755538</v>
       </c>
       <c r="G5" t="n">
-        <v>0.004254839454904571</v>
+        <v>0.005060147566467056</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8163151563330622</v>
+        <v>0.7955793945456492</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7181532225427338</v>
+        <v>0.8206202022535625</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8701291405168524</v>
+        <v>0.885819623470318</v>
       </c>
       <c r="K5" t="n">
-        <v>14.569</v>
+        <v>19.323</v>
       </c>
       <c r="L5" t="n">
-        <v>5.32</v>
+        <v>6.65</v>
       </c>
       <c r="M5" t="n">
-        <v>0.7708</v>
+        <v>0.8193</v>
       </c>
       <c r="N5" t="n">
-        <v>0.9262</v>
+        <v>0.9465</v>
       </c>
       <c r="O5" t="n">
-        <v>0.8734</v>
+        <v>0.9075</v>
       </c>
       <c r="P5" t="n">
-        <v>0.8329</v>
+        <v>0.7984</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.7173</v>
+        <v>0.8414</v>
       </c>
       <c r="R5" t="n">
-        <v>0.8752</v>
+        <v>0.8914</v>
       </c>
       <c r="S5" t="n">
-        <v>0.6858</v>
+        <v>0.7418</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2978</v>
+        <v>0.2923</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>MLP</t>
+          <t>EBM</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>balanced</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -819,66 +819,66 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.7638435817419618</v>
+        <v>0.8009504015452423</v>
       </c>
       <c r="E6" t="n">
-        <v>0.007048004886076593</v>
+        <v>0.005202682637965449</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9184766557449542</v>
+        <v>0.9373762069707006</v>
       </c>
       <c r="G6" t="n">
-        <v>0.004254839454904571</v>
+        <v>0.002621040993716543</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8163151563330622</v>
+        <v>0.8503856976864406</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7181532225427338</v>
+        <v>0.7571827964111664</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8701291405168524</v>
+        <v>0.8899463146989774</v>
       </c>
       <c r="K6" t="n">
-        <v>14.312</v>
+        <v>280.69</v>
       </c>
       <c r="L6" t="n">
-        <v>5</v>
+        <v>6.79</v>
       </c>
       <c r="M6" t="n">
-        <v>0.7708</v>
+        <v>0.8071</v>
       </c>
       <c r="N6" t="n">
-        <v>0.9262</v>
+        <v>0.9421</v>
       </c>
       <c r="O6" t="n">
-        <v>0.8734</v>
+        <v>0.8948</v>
       </c>
       <c r="P6" t="n">
-        <v>0.8329</v>
+        <v>0.8478</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.7173</v>
+        <v>0.7702</v>
       </c>
       <c r="R6" t="n">
-        <v>0.8752</v>
+        <v>0.8923</v>
       </c>
       <c r="S6" t="n">
-        <v>0.6858</v>
+        <v>0.7327</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2978</v>
+        <v>0.2654</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>MLP</t>
+          <t>EBM</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>smote</t>
+          <t>balanced</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -887,55 +887,55 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.7572306532482551</v>
+        <v>0.8009504015452423</v>
       </c>
       <c r="E7" t="n">
-        <v>0.008394077963791647</v>
+        <v>0.005202682637965449</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9096239909896064</v>
+        <v>0.9373762069707006</v>
       </c>
       <c r="G7" t="n">
-        <v>0.002737100653331916</v>
+        <v>0.002621040993716543</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7224095083836887</v>
+        <v>0.8503856976864406</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7967202255985899</v>
+        <v>0.7571827964111664</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8504606168418972</v>
+        <v>0.8899463146989774</v>
       </c>
       <c r="K7" t="n">
-        <v>30.771</v>
+        <v>428.258</v>
       </c>
       <c r="L7" t="n">
-        <v>5</v>
+        <v>6.65</v>
       </c>
       <c r="M7" t="n">
-        <v>0.7713</v>
+        <v>0.8071</v>
       </c>
       <c r="N7" t="n">
-        <v>0.9187</v>
+        <v>0.9421</v>
       </c>
       <c r="O7" t="n">
-        <v>0.8649</v>
+        <v>0.8948</v>
       </c>
       <c r="P7" t="n">
-        <v>0.7354000000000001</v>
+        <v>0.8478</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.8109</v>
+        <v>0.7702</v>
       </c>
       <c r="R7" t="n">
-        <v>0.8593</v>
+        <v>0.8923</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6701</v>
+        <v>0.7327</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3719</v>
+        <v>0.2654</v>
       </c>
     </row>
   </sheetData>
